--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486974_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486974_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.518</v>
+        <v>2.8538</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7048</v>
+        <v>0.237</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1869</v>
+        <v>2.6169</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0189</v>
+        <v>0.5875</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0544</v>
+        <v>-1.9333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.0732</v>
+        <v>2.5208</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8143</v>
+        <v>1.9755</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7748</v>
+        <v>-1.0764</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0395</v>
+        <v>3.0519</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8332</v>
+        <v>-1.388</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7204</v>
+        <v>-0.8569</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1127</v>
+        <v>-0.5311</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2321</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2588</v>
+        <v>3.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0646</v>
+        <v>0.0795</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1966</v>
+        <v>-0.4263</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.132</v>
+        <v>0.5058</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2402</v>
+        <v>2.1868</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7207</v>
+        <v>1.7679</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4805</v>
+        <v>0.4189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2723</v>
+        <v>2.7325</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5224</v>
+        <v>0.6878</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7947</v>
+        <v>2.0447</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5875</v>
+        <v>-2.1415</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9333</v>
+        <v>-0.597</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5208</v>
+        <v>-1.5445</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9755</v>
+        <v>-1.7322</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0764</v>
+        <v>-0.3241</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0519</v>
+        <v>-1.4081</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.388</v>
+        <v>-0.4094</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8569</v>
+        <v>-0.2729</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5311</v>
+        <v>-0.1364</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>1.6427</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0801</v>
+        <v>2.6694</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.502</v>
+        <v>-0.4833</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1857</v>
+        <v>-0.5697</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6837</v>
+        <v>0.0864</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1868</v>
+        <v>3.7146</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7679</v>
+        <v>4.0164</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4189</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0407</v>
+        <v>1.9193</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2035</v>
+        <v>2.1358</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8372</v>
+        <v>-0.2165</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.1415</v>
+        <v>-0.0189</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.597</v>
+        <v>1.0544</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5445</v>
+        <v>-1.0732</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.7322</v>
+        <v>1.8143</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3241</v>
+        <v>1.7748</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4081</v>
+        <v>0.0395</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4094</v>
+        <v>-1.8332</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2729</v>
+        <v>-0.7204</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1364</v>
+        <v>-1.1127</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6694</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.175</v>
+        <v>0.4659</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.054</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1211</v>
+        <v>-0.1616</v>
       </c>
       <c r="V4" t="n">
-        <v>3.7146</v>
+        <v>0.2402</v>
       </c>
       <c r="W4" t="n">
-        <v>4.0164</v>
+        <v>0.7207</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3018</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9522</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4591</v>
+        <v>-0.1669</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4112</v>
+        <v>1.1564</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8069</v>
+        <v>-1.0028</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5938</v>
+        <v>-0.9476</v>
       </c>
       <c r="I5" t="n">
-        <v>0.213</v>
+        <v>-0.0552</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5088</v>
+        <v>0.4802</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7855</v>
+        <v>0.4672</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2766</v>
+        <v>0.013</v>
       </c>
       <c r="M5" t="n">
-        <v>0.298</v>
+        <v>-1.483</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1917</v>
+        <v>-1.4148</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4897</v>
+        <v>-0.0682</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.828</v>
+        <v>-0.7594</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0931</v>
+        <v>-0.6471</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7348</v>
+        <v>-0.1122</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1786</v>
+        <v>0.6982</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7144</v>
+        <v>0.8978</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.442</v>
+        <v>-0.6024</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1564</v>
+        <v>1.5002</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0028</v>
+        <v>0.8069</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9476</v>
+        <v>0.5938</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0552</v>
+        <v>0.213</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4802</v>
+        <v>0.5088</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4672</v>
+        <v>0.7855</v>
       </c>
       <c r="L6" t="n">
-        <v>0.013</v>
+        <v>-0.2766</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.483</v>
+        <v>0.298</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4148</v>
+        <v>-0.1917</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0682</v>
+        <v>0.4897</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q6" t="n">
+        <v>-2.0534</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.8481</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.8824</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.2364</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.6459</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.0534</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1.0344</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.9222</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.1122</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.6982</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.6982</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4434</v>
+        <v>-0.0978</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5906</v>
+        <v>-1.1911</v>
       </c>
       <c r="F7" t="n">
-        <v>1.034</v>
+        <v>1.0933</v>
       </c>
       <c r="G7" t="n">
         <v>2.5235</v>
@@ -1000,13 +1000,13 @@
         <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4579</v>
+        <v>-0.0833</v>
       </c>
       <c r="T7" t="n">
-        <v>0.209</v>
+        <v>-0.3915</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2489</v>
+        <v>0.3082</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2793</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8159</v>
+        <v>-0.377</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0585</v>
+        <v>-1.6788</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2425</v>
+        <v>1.3018</v>
       </c>
       <c r="G8" t="n">
         <v>2.0568</v>
@@ -1078,13 +1078,13 @@
         <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5605</v>
+        <v>-1.1216</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9222</v>
+        <v>-0.5425</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6383</v>
+        <v>-0.579</v>
       </c>
       <c r="V8" t="n">
         <v>1.7679</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9331</v>
+        <v>-1.5517</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7495</v>
+        <v>-3.1606</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8164</v>
+        <v>1.6089</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9337</v>
@@ -1156,13 +1156,13 @@
         <v>3.2855</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6031</v>
+        <v>-0.2217</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3833</v>
+        <v>-0.7944</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7802</v>
+        <v>0.5727</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6283</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7537</v>
+        <v>-3.2694</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0426</v>
+        <v>-3.5583</v>
       </c>
       <c r="F10" t="n">
         <v>0.2888</v>
@@ -1234,10 +1234,10 @@
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0422</v>
+        <v>-0.5579</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8563</v>
+        <v>-0.3721</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1858</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.4383</v>
+        <v>4.096899999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.9564</v>
+        <v>-7.2975</v>
       </c>
       <c r="F11" t="n">
-        <v>11.3943</v>
+        <v>11.3945</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3143</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6974999999999998</v>
+        <v>0.6974999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-3.0117</v>
@@ -1288,7 +1288,7 @@
         <v>4.649</v>
       </c>
       <c r="K11" t="n">
-        <v>7.334899999999999</v>
+        <v>7.3349</v>
       </c>
       <c r="L11" t="n">
         <v>-2.6859</v>
@@ -1300,10 +1300,10 @@
         <v>-6.637499999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3258000000000003</v>
+        <v>-0.3258</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0268</v>
+        <v>1.026800000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-20.5341</v>
@@ -1312,10 +1312,10 @@
         <v>21.5609</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.222700000000001</v>
+        <v>-3.5642</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.0112</v>
+        <v>-3.3525</v>
       </c>
       <c r="U11" t="n">
         <v>-0.2113999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9897</v>
+        <v>5.4378</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0778</v>
+        <v>1.4962</v>
       </c>
       <c r="F12" t="n">
-        <v>3.9119</v>
+        <v>3.9416</v>
       </c>
       <c r="G12" t="n">
         <v>4.4649</v>
@@ -1390,13 +1390,13 @@
         <v>2.8748</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4382</v>
+        <v>0.8862</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.283</v>
+        <v>0.1354</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7212</v>
+        <v>0.7508</v>
       </c>
       <c r="V12" t="n">
         <v>0.7027</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5257</v>
+        <v>2.2869</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9194</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6063</v>
+        <v>1.5766</v>
       </c>
       <c r="G13" t="n">
         <v>1.0738</v>
@@ -1468,13 +1468,13 @@
         <v>3.0801</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7512</v>
+        <v>0.5123</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2749</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4763</v>
+        <v>0.4467</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7634</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4958</v>
+        <v>1.9532</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.014</v>
+        <v>-0.1255</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5098</v>
+        <v>2.0787</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7706</v>
+        <v>1.8746</v>
       </c>
       <c r="H14" t="n">
-        <v>0.876</v>
+        <v>1.5248</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.3498</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5278</v>
+        <v>2.8893</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8439</v>
+        <v>2.495</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.3943</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2428</v>
+        <v>-1.0147</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0321</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2107</v>
+        <v>-0.0445</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.2855</v>
+        <v>-2.4641</v>
       </c>
       <c r="R14" t="n">
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0964</v>
+        <v>0.4581</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9141</v>
+        <v>-0.2017</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1823</v>
+        <v>0.6597</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7552</v>
+        <v>-0.5848</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8295</v>
+        <v>-0.3491</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5848</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4458</v>
+        <v>1.4968</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.7462</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9898</v>
+        <v>2.243</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8746</v>
+        <v>1.7706</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5248</v>
+        <v>0.876</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3498</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8893</v>
+        <v>1.5278</v>
       </c>
       <c r="K15" t="n">
-        <v>2.495</v>
+        <v>0.8439</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3943</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0147</v>
+        <v>0.2428</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9703000000000001</v>
+        <v>0.0321</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0445</v>
+        <v>0.2107</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4641</v>
+        <v>-3.2855</v>
       </c>
       <c r="R15" t="n">
         <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0493</v>
+        <v>1.0974</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6201</v>
+        <v>0.1819</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5708</v>
+        <v>0.9155</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5848</v>
+        <v>-0.7552</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3491</v>
+        <v>0.8295</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2357</v>
+        <v>-1.5848</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3357</v>
+        <v>0.9486</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8006</v>
+        <v>0.5914</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5351</v>
+        <v>0.3573</v>
       </c>
       <c r="G16" t="n">
         <v>3.6015</v>
@@ -1702,13 +1702,13 @@
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1794</v>
+        <v>0.7923</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6778</v>
+        <v>0.4686</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.3237</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8025</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.535</v>
+        <v>-0.5037</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8839</v>
+        <v>-0.6747</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3489</v>
+        <v>0.171</v>
       </c>
       <c r="G17" t="n">
         <v>0.3043</v>
@@ -1780,13 +1780,13 @@
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2812</v>
+        <v>-0.2499</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4534</v>
+        <v>-0.2442</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1722</v>
+        <v>-0.0057</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5848</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5361</v>
+        <v>-1.2101</v>
       </c>
       <c r="E18" t="n">
         <v>-2.3262</v>
       </c>
       <c r="F18" t="n">
-        <v>0.79</v>
+        <v>1.1161</v>
       </c>
       <c r="G18" t="n">
         <v>-4.1802</v>
@@ -1858,13 +1858,13 @@
         <v>2.8748</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2637</v>
+        <v>0.5898</v>
       </c>
       <c r="T18" t="n">
         <v>0.1431</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1206</v>
+        <v>0.4467</v>
       </c>
       <c r="V18" t="n">
         <v>0.9429</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.813</v>
+        <v>-4.0989</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2527</v>
+        <v>-2.7757</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5603</v>
+        <v>-1.3232</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5212</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4679</v>
+        <v>0.1821</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8677</v>
+        <v>0.3447</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3998</v>
+        <v>-0.1626</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5277</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0605</v>
+        <v>-4.8521</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.476</v>
+        <v>-5.1725</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5845</v>
+        <v>0.3203</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9424</v>
+        <v>-3.1316</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1872</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7552</v>
+        <v>-2.2813</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9692</v>
+        <v>-1.759</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7718</v>
+        <v>0.1752</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1974</v>
+        <v>-1.9342</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0268</v>
+        <v>-1.3726</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4154</v>
+        <v>-1.0255</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4422</v>
+        <v>-0.3472</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2321</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5029</v>
+        <v>0.2935</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4534</v>
+        <v>-0.3333</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0495</v>
+        <v>0.6268</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4098</v>
+        <v>-0.1659</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.5884</v>
+        <v>-0.1659</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2862</v>
+        <v>-4.8966</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.6955</v>
+        <v>-2.3714</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4092</v>
+        <v>-2.5252</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1316</v>
+        <v>-1.9424</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-1.1872</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2813</v>
+        <v>-0.7552</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.759</v>
+        <v>-1.9692</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1752</v>
+        <v>-0.7718</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9342</v>
+        <v>-1.1974</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3726</v>
+        <v>0.0268</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0255</v>
+        <v>-0.4154</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3472</v>
+        <v>0.4422</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8481</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0801</v>
+        <v>-1.2321</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1406</v>
+        <v>-0.339</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8563</v>
+        <v>-0.3488</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7157</v>
+        <v>0.0098</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1659</v>
+        <v>-2.4098</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1659</v>
+        <v>-3.5884</v>
       </c>
     </row>
     <row r="22">
@@ -2134,7 +2134,7 @@
         <v>7.956200000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>2.314300000000001</v>
+        <v>2.3143</v>
       </c>
       <c r="H22" t="n">
         <v>-0.6971999999999999</v>
@@ -2143,7 +2143,7 @@
         <v>3.0118</v>
       </c>
       <c r="J22" t="n">
-        <v>6.963199999999999</v>
+        <v>6.9632</v>
       </c>
       <c r="K22" t="n">
         <v>6.637500000000001</v>
@@ -2152,7 +2152,7 @@
         <v>0.3257000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.648899999999999</v>
+        <v>-4.6489</v>
       </c>
       <c r="N22" t="n">
         <v>-7.3349</v>
@@ -2173,13 +2173,13 @@
         <v>4.222799999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2114000000000001</v>
+        <v>0.2114</v>
       </c>
       <c r="U22" t="n">
-        <v>4.011299999999999</v>
+        <v>4.0114</v>
       </c>
       <c r="V22" t="n">
-        <v>-8.948500000000001</v>
+        <v>-8.948499999999999</v>
       </c>
       <c r="W22" t="n">
         <v>2.9916</v>
